--- a/artfynd/A 64082-2023 artfynd.xlsx
+++ b/artfynd/A 64082-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64082-2023 artfynd.xlsx
+++ b/artfynd/A 64082-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114560407</v>
       </c>
       <c r="B2" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,6 +778,324 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114560353</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>352145</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6422248</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114560226</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>352151</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6422241</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114560420</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>352143</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6422222</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64082-2023 artfynd.xlsx
+++ b/artfynd/A 64082-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560407</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560353</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560226</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560420</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>